--- a/01_게임_기획/05_밸런스/outputs/2026-10-08_도깨비_조합/도깨비_스킬_밸런스.xlsx
+++ b/01_게임_기획/05_밸런스/outputs/2026-10-08_도깨비_조합/도깨비_스킬_밸런스.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용안내" sheetId="1" r:id="Rf34e342e095a4a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="2" r:id="R42ea54e559c74e3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="3" r:id="R72ba5a392b394fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recipes" sheetId="4" r:id="R0385724d1a604dd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enhancements" sheetId="5" r:id="R6ead798e894546a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branches" sheetId="6" r:id="R3aecbcd33f2a4b68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용안내" sheetId="1" r:id="R1fbee2d5f5864cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="2" r:id="R3ddf425c085f4ae0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="3" r:id="Rb7a854274f80431b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recipes" sheetId="4" r:id="R1a26e20adfde4683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enhancements" sheetId="5" r:id="R8a3d254b18d14026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branches" sheetId="6" r:id="Redd71cd412e749ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -446,7 +446,7 @@
         <x:v>쿨타임</x:v>
       </x:c>
       <x:c r="B9" s="2" t="str">
-        <x:v>첫 입력 승인부터 계산. 연계 중에는 다음 타만 허용.</x:v>
+        <x:v>Q1부터 공통 기본 10초. Q1·Q2 사용마다 다음 타 대기 6초.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
@@ -541,10 +541,10 @@
         <x:v>연계 횟수</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>공유 쿨타임</x:v>
+        <x:v>공통 기본 쿨타임</x:v>
       </x:c>
       <x:c r="E2" s="10" t="str">
-        <x:v>다음 입력 유예</x:v>
+        <x:v>다음 타 대기 제한</x:v>
       </x:c>
       <x:c r="F2" s="10" t="str">
         <x:v>선입력 허용</x:v>
@@ -587,10 +587,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="18" t="n">
-        <x:v>4.5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="18" t="n">
-        <x:v>1.2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F4" s="18" t="n">
         <x:v>0.18</x:v>
@@ -610,10 +610,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="18" t="n">
-        <x:v>5.5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="18" t="n">
-        <x:v>1.2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F5" s="18" t="n">
         <x:v>0.18</x:v>
@@ -633,10 +633,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="18" t="n">
-        <x:v>6.5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" s="18" t="n">
-        <x:v>1.2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F6" s="18" t="n">
         <x:v>0.18</x:v>
